--- a/data/trans_bre/IP16B02-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16B02-Estudios-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-36,08; 26,12</t>
+          <t>-35,17; 22,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-38,2; 26,55</t>
+          <t>-38,77; 23,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-74,29; -11,89</t>
+          <t>-76,93; -17,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-37,33; 37,85</t>
+          <t>-36,02; 29,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-40,73; 38,5</t>
+          <t>-42,89; 29,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-74,29; -11,89</t>
+          <t>-76,93; -17,88</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-27,86; 1,63</t>
+          <t>-28,68; 2,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-23,16; -0,69</t>
+          <t>-23,3; 0,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,62; 13,23</t>
+          <t>-10,76; 12,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-29,6; 1,95</t>
+          <t>-31,0; 3,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-25,1; -0,85</t>
+          <t>-25,83; 0,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,49; 16,47</t>
+          <t>-11,69; 14,94</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-40,28; 15,99</t>
+          <t>-36,57; 15,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 30,97</t>
+          <t>-7,46; 35,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-32,55; 5,98</t>
+          <t>-30,06; 6,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-44,98; 19,12</t>
+          <t>-38,79; 19,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 48,03</t>
+          <t>-7,62; 59,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-33,76; 6,23</t>
+          <t>-32,53; 7,1</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-21,46; 3,17</t>
+          <t>-21,5; 2,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,15; 2,94</t>
+          <t>-16,6; 3,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-17,91; 1,57</t>
+          <t>-17,29; 2,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,04; 3,57</t>
+          <t>-23,51; 3,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18,73; 3,24</t>
+          <t>-18,43; 3,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,71; 1,78</t>
+          <t>-18,78; 3,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16B02-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16B02-Estudios-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-35,17; 22,06</t>
+          <t>-36,48; 27,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-38,77; 23,43</t>
+          <t>-37,9; 26,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-76,93; -17,88</t>
+          <t>-73,76; -11,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-36,02; 29,34</t>
+          <t>-38,27; 40,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-42,89; 29,06</t>
+          <t>-41,36; 42,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-76,93; -17,88</t>
+          <t>-73,76; -11,55</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-28,68; 2,91</t>
+          <t>-27,27; 3,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-23,3; 0,35</t>
+          <t>-23,98; 0,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 12,37</t>
+          <t>-11,2; 12,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-31,0; 3,07</t>
+          <t>-29,81; 4,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-25,83; 0,33</t>
+          <t>-25,9; -0,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-11,69; 14,94</t>
+          <t>-11,94; 15,63</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-36,57; 15,94</t>
+          <t>-37,79; 15,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 35,46</t>
+          <t>-7,37; 31,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-30,06; 6,72</t>
+          <t>-33,34; 7,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-38,79; 19,2</t>
+          <t>-41,27; 18,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 59,64</t>
+          <t>-7,5; 50,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-32,53; 7,1</t>
+          <t>-35,33; 8,13</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-21,5; 2,93</t>
+          <t>-20,92; 2,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,6; 3,08</t>
+          <t>-16,78; 2,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-17,29; 2,8</t>
+          <t>-17,94; 2,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,51; 3,34</t>
+          <t>-23,61; 2,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18,43; 3,31</t>
+          <t>-18,46; 2,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,78; 3,19</t>
+          <t>-19,2; 2,48</t>
         </is>
       </c>
     </row>
